--- a/ponderaciones.xlsx
+++ b/ponderaciones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jgrijalazp\DAW\DIIW (diseno)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3475950-1F52-430A-94C1-39137C9FD7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56DEE838-6956-4C20-834D-8AA02965BA67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UT1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
   <si>
     <t>Pega esta hoja en otra que tengas y coloca tus notas en las casillas claras.</t>
   </si>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t>Práctico</t>
+  </si>
+  <si>
+    <t>47.2</t>
   </si>
 </sst>
 </file>
@@ -530,6 +533,54 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -545,62 +596,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -909,12 +912,12 @@
       <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="18"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="34"/>
     </row>
     <row r="5" spans="1:4" ht="22.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
@@ -931,10 +934,18 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7"/>
+      <c r="A6" s="6">
+        <v>100</v>
+      </c>
+      <c r="B6" s="6">
+        <v>100</v>
+      </c>
+      <c r="C6" s="6">
+        <v>50</v>
+      </c>
+      <c r="D6" s="7">
+        <v>90</v>
+      </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
@@ -943,10 +954,10 @@
       <c r="B7" s="9">
         <v>0</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="20"/>
+      <c r="D7" s="36"/>
     </row>
     <row r="8" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
@@ -955,22 +966,24 @@
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="34"/>
     </row>
     <row r="10" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6"/>
+      <c r="B10" s="6">
+        <v>45</v>
+      </c>
       <c r="C10" s="10">
         <v>0.2</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="30" t="s">
         <v>10</v>
       </c>
     </row>
@@ -978,21 +991,23 @@
       <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="6"/>
+      <c r="B11" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="C11" s="10">
         <v>0.1</v>
       </c>
-      <c r="D11" s="22"/>
+      <c r="D11" s="37"/>
     </row>
     <row r="12" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="38">
         <v>0</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="23"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="31"/>
     </row>
     <row r="13" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
@@ -1001,20 +1016,22 @@
       <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="18"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="34"/>
     </row>
     <row r="15" spans="1:4" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="6"/>
+      <c r="B15" s="6">
+        <v>47</v>
+      </c>
       <c r="C15" s="12"/>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="30" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1026,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="13"/>
-      <c r="D16" s="23"/>
+      <c r="D16" s="31"/>
     </row>
     <row r="17" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
@@ -1069,126 +1086,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="36"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="26"/>
     </row>
     <row r="2" spans="1:4" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
     </row>
     <row r="4" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="20">
         <v>0</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="27"/>
+      <c r="D4" s="17"/>
     </row>
     <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="31"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="36"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="26"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26" t="s">
+    <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="37" t="s">
+      <c r="B7" s="19"/>
+      <c r="C7" s="27" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="20">
         <v>0</v>
       </c>
-      <c r="C8" s="38"/>
+      <c r="C8" s="28"/>
       <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="36"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="26"/>
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="27" t="s">
         <v>15</v>
       </c>
       <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="39"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="29"/>
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="20">
         <v>0</v>
       </c>
-      <c r="C13" s="38"/>
+      <c r="C13" s="28"/>
       <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="31"/>
-      <c r="B14" s="31"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="20">
         <v>0</v>
       </c>
       <c r="C15" s="1"/>
